--- a/William MD80 Files/DesconLampe4138.xlsx
+++ b/William MD80 Files/DesconLampe4138.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/williamlampe/Documents/GitHub/ASEN4138_AircraftDesign/William MD80 Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF13E12A-C3A3-0645-9F6D-7AEC6160956B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CB1779-D05B-ED42-ABC2-A0815DDC9699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="1" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="243">
   <si>
     <t>Length_f</t>
   </si>
@@ -1070,32 +1070,32 @@
     <t>Prop_Dia</t>
   </si>
   <si>
-    <t>all stats -&gt; after are for per engine</t>
-  </si>
-  <si>
-    <t>Prop -&gt; jet = 0</t>
-  </si>
-  <si>
-    <t>Turbocharge is from sea level to 8,000 ft</t>
-  </si>
-  <si>
-    <t>Electric -&gt; jet = 0</t>
-  </si>
-  <si>
-    <t>MD80</t>
-  </si>
-  <si>
     <t>DSMA-523A</t>
   </si>
   <si>
     <t>NACA 0004</t>
+  </si>
+  <si>
+    <t>MD80_1</t>
+  </si>
+  <si>
+    <t>MD80_2</t>
+  </si>
+  <si>
+    <t>MD80_3</t>
+  </si>
+  <si>
+    <t>MD80_4</t>
+  </si>
+  <si>
+    <t>MD80_5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1142,6 +1142,13 @@
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1224,7 +1231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1247,11 +1254,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1319,7 +1339,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3335,7 +3360,7 @@
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>210</v>
@@ -3488,8 +3513,620 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F3" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G3" s="4">
+        <v>15</v>
+      </c>
+      <c r="H3" s="4">
+        <f>F3/G3</f>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I3" s="4">
+        <f>0.25*PI()*(G3)^2</f>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <f>PI()*G3*F3</f>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L3" s="4">
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>1209</v>
+      </c>
+      <c r="O3" s="4">
+        <v>2500</v>
+      </c>
+      <c r="P3" s="4">
+        <f>(107.67717^2)/N3</f>
+        <v>9.5900520588990084</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R3" s="4">
+        <v>35</v>
+      </c>
+      <c r="S3" s="4">
+        <v>30</v>
+      </c>
+      <c r="T3" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U3" s="4">
+        <f>0.25*N3</f>
+        <v>302.25</v>
+      </c>
+      <c r="V3" s="4">
+        <f>2*U3</f>
+        <v>604.5</v>
+      </c>
+      <c r="W3" s="4">
+        <f>((107.67717/3)^2)/U3</f>
+        <v>4.2622453595106693</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="Y3" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z3" s="4">
+        <f>(15+(15*0.4))/2</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <v>302.25</v>
+      </c>
+      <c r="AJ3" s="4">
+        <v>604.5</v>
+      </c>
+      <c r="AK3" s="4">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL3" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="4">
+        <v>35</v>
+      </c>
+      <c r="AN3" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AO3" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F4" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G4" s="4">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4">
+        <f>F4/G4</f>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I4" s="4">
+        <f>0.25*PI()*(G4)^2</f>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <f>PI()*G4*F4</f>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1209</v>
+      </c>
+      <c r="O4" s="4">
+        <v>2500</v>
+      </c>
+      <c r="P4" s="4">
+        <f>(107.67717^2)/N4</f>
+        <v>9.5900520588990084</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R4" s="4">
+        <v>35</v>
+      </c>
+      <c r="S4" s="4">
+        <v>30</v>
+      </c>
+      <c r="T4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U4" s="4">
+        <f>0.25*N4</f>
+        <v>302.25</v>
+      </c>
+      <c r="V4" s="4">
+        <f>2*U4</f>
+        <v>604.5</v>
+      </c>
+      <c r="W4" s="4">
+        <f>((107.67717/3)^2)/U4</f>
+        <v>4.2622453595106693</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="Y4" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z4" s="4">
+        <f>(15+(15*0.4))/2</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="4">
+        <v>302.25</v>
+      </c>
+      <c r="AJ4" s="4">
+        <v>604.5</v>
+      </c>
+      <c r="AK4" s="4">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL4" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="4">
+        <v>35</v>
+      </c>
+      <c r="AN4" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AO4" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F5" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G5" s="4">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4">
+        <f>F5/G5</f>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I5" s="4">
+        <f>0.25*PI()*(G5)^2</f>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <f>PI()*G5*F5</f>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L5" s="4">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4">
+        <v>2</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1209</v>
+      </c>
+      <c r="O5" s="4">
+        <v>2500</v>
+      </c>
+      <c r="P5" s="4">
+        <f>(107.67717^2)/N5</f>
+        <v>9.5900520588990084</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R5" s="4">
+        <v>35</v>
+      </c>
+      <c r="S5" s="4">
+        <v>30</v>
+      </c>
+      <c r="T5" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U5" s="4">
+        <f>0.25*N5</f>
+        <v>302.25</v>
+      </c>
+      <c r="V5" s="4">
+        <f>2*U5</f>
+        <v>604.5</v>
+      </c>
+      <c r="W5" s="4">
+        <f>((107.67717/3)^2)/U5</f>
+        <v>4.2622453595106693</v>
+      </c>
+      <c r="X5" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="Y5" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z5" s="4">
+        <f>(15+(15*0.4))/2</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="4">
+        <v>302.25</v>
+      </c>
+      <c r="AJ5" s="4">
+        <v>604.5</v>
+      </c>
+      <c r="AK5" s="4">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL5" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM5" s="4">
+        <v>35</v>
+      </c>
+      <c r="AN5" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AO5" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="30">
+        <v>0</v>
+      </c>
+      <c r="D6" s="30">
+        <v>0.76</v>
+      </c>
+      <c r="E6" s="30">
+        <v>0.76</v>
+      </c>
+      <c r="F6" s="30">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G6" s="30">
+        <v>15</v>
+      </c>
+      <c r="H6" s="30">
+        <v>9.8447069999999997</v>
+      </c>
+      <c r="I6" s="30">
+        <v>176.71459999999999</v>
+      </c>
+      <c r="J6" s="30">
+        <v>0</v>
+      </c>
+      <c r="K6" s="30">
+        <v>6958.8130000000001</v>
+      </c>
+      <c r="L6" s="30">
+        <v>1</v>
+      </c>
+      <c r="M6" s="30">
+        <v>2</v>
+      </c>
+      <c r="N6" s="30">
+        <v>1209</v>
+      </c>
+      <c r="O6" s="30">
+        <v>2500</v>
+      </c>
+      <c r="P6" s="30">
+        <v>9.590052</v>
+      </c>
+      <c r="Q6" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="R6" s="30">
+        <v>35</v>
+      </c>
+      <c r="S6" s="30">
+        <v>30</v>
+      </c>
+      <c r="T6" s="30">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U6" s="30">
+        <v>302.25</v>
+      </c>
+      <c r="V6" s="30">
+        <v>604.5</v>
+      </c>
+      <c r="W6" s="30">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="X6" s="30">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" s="30">
+        <v>35</v>
+      </c>
+      <c r="Z6" s="30">
+        <v>10.5</v>
+      </c>
+      <c r="AA6" s="30">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="30">
+        <v>302.25</v>
+      </c>
+      <c r="AJ6" s="30">
+        <v>604.5</v>
+      </c>
+      <c r="AK6" s="30">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL6" s="30">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="30">
+        <v>35</v>
+      </c>
+      <c r="AN6" s="30">
+        <v>10.5</v>
+      </c>
+      <c r="AO6" s="30">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="30">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="30">
+        <v>0</v>
+      </c>
+    </row>
     <row r="16" spans="1:48" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -3498,7 +4135,7 @@
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B5:B15</xm:sqref>
+          <xm:sqref>B7:B15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3692,10 +4329,10 @@
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C2" s="10">
         <v>0.11</v>
@@ -3819,7 +4456,7 @@
         <v>6.3699999999999998E-3</v>
       </c>
       <c r="AQ2" s="10" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AR2" s="10">
         <v>0.04</v>
@@ -3856,34 +4493,664 @@
       </c>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.2">
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
-      <c r="S3"/>
-      <c r="T3"/>
-      <c r="V3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
-      <c r="AH3"/>
-      <c r="AI3"/>
-      <c r="AJ3"/>
-      <c r="AL3"/>
-      <c r="AM3"/>
-      <c r="AN3"/>
-      <c r="AO3"/>
+      <c r="A3" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E3" s="10">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F3" s="10">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G3" s="10">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H3" s="10">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P3" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R3" s="10">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S3" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T3" s="10">
+        <v>1.4271</v>
+      </c>
+      <c r="U3" s="10">
+        <v>1.5059</v>
+      </c>
+      <c r="V3" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="W3" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="X3" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z3" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA3" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB3" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC3" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD3" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE3" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG3" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH3" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI3" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ3" s="10">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK3" s="10">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL3" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP3" s="10">
+        <f>MIN(X3:AO3)</f>
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ3" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR3" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AS3" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX3" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AY3" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E4" s="10">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F4" s="10">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G4" s="10">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H4" s="10">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J4" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L4" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N4" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O4" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P4" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q4" s="10">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R4" s="10">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S4" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T4" s="10">
+        <v>1.4271</v>
+      </c>
+      <c r="U4" s="10">
+        <v>1.5059</v>
+      </c>
+      <c r="V4" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="W4" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="X4" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y4" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z4" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA4" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB4" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC4" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD4" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE4" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF4" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG4" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH4" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI4" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ4" s="10">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK4" s="10">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL4" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM4" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN4" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO4" s="10">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP4" s="10">
+        <f>MIN(X4:AO4)</f>
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ4" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR4" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AS4" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX4" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AY4" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E5" s="10">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F5" s="10">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G5" s="10">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H5" s="10">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P5" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R5" s="10">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S5" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T5" s="10">
+        <v>1.4271</v>
+      </c>
+      <c r="U5" s="10">
+        <v>1.5059</v>
+      </c>
+      <c r="V5" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="W5" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="X5" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI5" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ5" s="10">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM5" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN5" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO5" s="10">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP5" s="10">
+        <f>MIN(X5:AO5)</f>
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ5" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR5" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AS5" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX5" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AY5" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E6" s="10">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F6" s="10">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G6" s="10">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H6" s="10">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J6" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K6" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O6" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P6" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R6" s="10">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S6" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T6" s="10">
+        <v>1.4271</v>
+      </c>
+      <c r="U6" s="10">
+        <v>1.5059</v>
+      </c>
+      <c r="V6" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="W6" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="X6" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB6" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC6" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD6" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE6" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF6" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI6" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ6" s="10">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK6" s="10">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM6" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN6" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO6" s="10">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP6" s="10">
+        <f>MIN(X6:AO6)</f>
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ6" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR6" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AS6" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX6" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AY6" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:54" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
@@ -3963,7 +5230,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B2" t="s">
         <v>185</v>
@@ -4017,27 +5284,233 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>19500</v>
+      </c>
+      <c r="E3">
+        <v>0.73</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>19500</v>
+      </c>
+      <c r="E4">
+        <v>0.73</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>19500</v>
+      </c>
+      <c r="E5">
+        <v>0.73</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="D6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H6" s="29">
+      <c r="A6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>19500</v>
+      </c>
+      <c r="E6">
+        <v>0.73</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>0.2</v>
       </c>
-      <c r="I6" t="s">
-        <v>237</v>
-      </c>
-      <c r="M6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="D7" t="s">
-        <v>238</v>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18" s="20" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
   <extLst>
@@ -4047,7 +5520,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B5:B15 B2</xm:sqref>
+          <xm:sqref>B2:B15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/William MD80 Files/DesconLampe4138.xlsx
+++ b/William MD80 Files/DesconLampe4138.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/williamlampe/Documents/GitHub/ASEN4138_AircraftDesign/William MD80 Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/williamlampe/Documents/MATLAB/ASEN 4138/AES-AircraftDesignToolbox/MAIN/Input Excel Sheets/Design Configurations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CB1779-D05B-ED42-ABC2-A0815DDC9699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5FAD94-040A-DC48-B310-141D4651858C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="1" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
@@ -281,7 +281,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -290,12 +290,31 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Units of lb/hr/hp
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Units of lb/hr/hp
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
 </t>
         </r>
       </text>
@@ -360,7 +379,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="248">
   <si>
     <t>Length_f</t>
   </si>
@@ -1089,6 +1108,21 @@
   </si>
   <si>
     <t>MD80_5</t>
+  </si>
+  <si>
+    <t>MD80_6</t>
+  </si>
+  <si>
+    <t>MD80_7</t>
+  </si>
+  <si>
+    <t>MD80_8</t>
+  </si>
+  <si>
+    <t>MD80_9</t>
+  </si>
+  <si>
+    <t>MD80_10</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1339,11 +1373,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3399,17 +3430,18 @@
         <v>1</v>
       </c>
       <c r="M2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" s="4">
-        <v>1209</v>
+        <v>850</v>
       </c>
       <c r="O2" s="4">
-        <v>2500</v>
+        <f>2*N2-G2*(2*N2/(SQRT(P2*N2)*(1+Q2)))*2</f>
+        <v>1270.5263157894738</v>
       </c>
       <c r="P2" s="4">
-        <f>(107.67717^2)/N2</f>
-        <v>9.5900520588990084</v>
+        <f>(95^2)/N2</f>
+        <v>10.617647058823529</v>
       </c>
       <c r="Q2" s="4">
         <v>0.25</v>
@@ -3425,15 +3457,15 @@
       </c>
       <c r="U2" s="4">
         <f>0.25*N2</f>
-        <v>302.25</v>
+        <v>212.5</v>
       </c>
       <c r="V2" s="4">
         <f>2*U2</f>
-        <v>604.5</v>
+        <v>425</v>
       </c>
       <c r="W2" s="4">
         <f>((107.67717/3)^2)/U2</f>
-        <v>4.2622453595106693</v>
+        <v>6.062417223115764</v>
       </c>
       <c r="X2" s="4">
         <v>0.4</v>
@@ -3554,17 +3586,18 @@
         <v>1</v>
       </c>
       <c r="M3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>1209</v>
+        <v>900</v>
       </c>
       <c r="O3" s="4">
-        <v>2500</v>
+        <f t="shared" ref="O3:O5" si="0">2*N3-G3*(2*N3/(SQRT(P3*N3)*(1+Q3)))*2</f>
+        <v>1345.2631578947369</v>
       </c>
       <c r="P3" s="4">
-        <f>(107.67717^2)/N3</f>
-        <v>9.5900520588990084</v>
+        <f t="shared" ref="P3:P11" si="1">(95^2)/N3</f>
+        <v>10.027777777777779</v>
       </c>
       <c r="Q3" s="4">
         <v>0.25</v>
@@ -3580,15 +3613,15 @@
       </c>
       <c r="U3" s="4">
         <f>0.25*N3</f>
-        <v>302.25</v>
+        <v>225</v>
       </c>
       <c r="V3" s="4">
         <f>2*U3</f>
-        <v>604.5</v>
+        <v>450</v>
       </c>
       <c r="W3" s="4">
         <f>((107.67717/3)^2)/U3</f>
-        <v>4.2622453595106693</v>
+        <v>5.725616266276</v>
       </c>
       <c r="X3" s="4">
         <v>0.4</v>
@@ -3709,17 +3742,18 @@
         <v>1</v>
       </c>
       <c r="M4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>1209</v>
+        <v>950</v>
       </c>
       <c r="O4" s="4">
-        <v>2500</v>
+        <f t="shared" si="0"/>
+        <v>1420</v>
       </c>
       <c r="P4" s="4">
-        <f>(107.67717^2)/N4</f>
-        <v>9.5900520588990084</v>
+        <f t="shared" si="1"/>
+        <v>9.5</v>
       </c>
       <c r="Q4" s="4">
         <v>0.25</v>
@@ -3735,15 +3769,15 @@
       </c>
       <c r="U4" s="4">
         <f>0.25*N4</f>
-        <v>302.25</v>
+        <v>237.5</v>
       </c>
       <c r="V4" s="4">
         <f>2*U4</f>
-        <v>604.5</v>
+        <v>475</v>
       </c>
       <c r="W4" s="4">
         <f>((107.67717/3)^2)/U4</f>
-        <v>4.2622453595106693</v>
+        <v>5.4242680417351572</v>
       </c>
       <c r="X4" s="4">
         <v>0.4</v>
@@ -3864,17 +3898,18 @@
         <v>1</v>
       </c>
       <c r="M5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>1209</v>
+        <v>1000</v>
       </c>
       <c r="O5" s="4">
-        <v>2500</v>
+        <f t="shared" si="0"/>
+        <v>1494.7368421052631</v>
       </c>
       <c r="P5" s="4">
-        <f>(107.67717^2)/N5</f>
-        <v>9.5900520588990084</v>
+        <f t="shared" si="1"/>
+        <v>9.0250000000000004</v>
       </c>
       <c r="Q5" s="4">
         <v>0.25</v>
@@ -3890,15 +3925,15 @@
       </c>
       <c r="U5" s="4">
         <f>0.25*N5</f>
-        <v>302.25</v>
+        <v>250</v>
       </c>
       <c r="V5" s="4">
         <f>2*U5</f>
-        <v>604.5</v>
+        <v>500</v>
       </c>
       <c r="W5" s="4">
         <f>((107.67717/3)^2)/U5</f>
-        <v>4.2622453595106693</v>
+        <v>5.1530546396484</v>
       </c>
       <c r="X5" s="4">
         <v>0.4</v>
@@ -3979,148 +4014,938 @@
       </c>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="30">
-        <v>0</v>
-      </c>
-      <c r="D6" s="30">
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
         <v>0.76</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="4">
         <v>0.76</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="4">
         <v>147.67060000000001</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="4">
         <v>15</v>
       </c>
-      <c r="H6" s="30">
-        <v>9.8447069999999997</v>
-      </c>
-      <c r="I6" s="30">
-        <v>176.71459999999999</v>
-      </c>
-      <c r="J6" s="30">
-        <v>0</v>
-      </c>
-      <c r="K6" s="30">
-        <v>6958.8130000000001</v>
-      </c>
-      <c r="L6" s="30">
+      <c r="H6" s="4">
+        <f>F6/G6</f>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I6" s="4">
+        <f>0.25*PI()*(G6)^2</f>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
+        <f>PI()*G6*F6</f>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L6" s="4">
         <v>1</v>
       </c>
-      <c r="M6" s="30">
+      <c r="M6" s="4">
+        <v>1</v>
+      </c>
+      <c r="N6" s="4">
+        <v>1050</v>
+      </c>
+      <c r="O6" s="4">
+        <f>2*N6-G6*(2*N6/(SQRT(P6*N6)*(1+Q6)))*2</f>
+        <v>1569.4736842105262</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5952380952380949</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R6" s="4">
+        <v>35</v>
+      </c>
+      <c r="S6" s="4">
+        <v>30</v>
+      </c>
+      <c r="T6" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U6" s="4">
+        <f>0.25*N6</f>
+        <v>262.5</v>
+      </c>
+      <c r="V6" s="4">
+        <f>2*U6</f>
+        <v>525</v>
+      </c>
+      <c r="W6" s="4">
+        <f>((107.67717/3)^2)/U6</f>
+        <v>4.9076710853794285</v>
+      </c>
+      <c r="X6" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="Y6" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z6" s="4">
+        <f>(15+(15*0.4))/2</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA6" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="4">
+        <v>302.25</v>
+      </c>
+      <c r="AJ6" s="4">
+        <v>604.5</v>
+      </c>
+      <c r="AK6" s="4">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL6" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="4">
+        <v>35</v>
+      </c>
+      <c r="AN6" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AO6" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F7" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G7" s="4">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" ref="H7:H11" si="2">F7/G7</f>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I7" s="4">
+        <f t="shared" ref="I7:I11" si="3">0.25*PI()*(G7)^2</f>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" ref="K7:K11" si="4">PI()*G7*F7</f>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L7" s="4">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1100</v>
+      </c>
+      <c r="O7" s="4">
+        <f t="shared" ref="O7:O11" si="5">2*N7-G7*(2*N7/(SQRT(P7*N7)*(1+Q7)))*2</f>
+        <v>1644.2105263157896</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="1"/>
+        <v>8.204545454545455</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R7" s="4">
+        <v>35</v>
+      </c>
+      <c r="S7" s="4">
+        <v>30</v>
+      </c>
+      <c r="T7" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U7" s="4">
+        <f t="shared" ref="U7:U11" si="6">0.25*N7</f>
+        <v>275</v>
+      </c>
+      <c r="V7" s="4">
+        <f t="shared" ref="V7:V11" si="7">2*U7</f>
+        <v>550</v>
+      </c>
+      <c r="W7" s="4">
+        <f t="shared" ref="W7:W11" si="8">((107.67717/3)^2)/U7</f>
+        <v>4.6845951269530905</v>
+      </c>
+      <c r="X7" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="Y7" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" ref="Z7:Z11" si="9">(15+(15*0.4))/2</f>
+        <v>10.5</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>302.25</v>
+      </c>
+      <c r="AJ7" s="4">
+        <v>604.5</v>
+      </c>
+      <c r="AK7" s="4">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM7" s="4">
+        <v>35</v>
+      </c>
+      <c r="AN7" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AO7" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F8" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G8" s="4">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="2"/>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="3"/>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J8" s="4">
         <v>2</v>
       </c>
-      <c r="N6" s="30">
-        <v>1209</v>
-      </c>
-      <c r="O6" s="30">
-        <v>2500</v>
-      </c>
-      <c r="P6" s="30">
-        <v>9.590052</v>
-      </c>
-      <c r="Q6" s="30">
+      <c r="K8" s="4">
+        <f t="shared" si="4"/>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L8" s="4">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4">
+        <v>1150</v>
+      </c>
+      <c r="O8" s="4">
+        <f t="shared" si="5"/>
+        <v>1718.9473684210525</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="1"/>
+        <v>7.8478260869565215</v>
+      </c>
+      <c r="Q8" s="4">
         <v>0.25</v>
       </c>
-      <c r="R6" s="30">
+      <c r="R8" s="4">
         <v>35</v>
       </c>
-      <c r="S6" s="30">
+      <c r="S8" s="4">
         <v>30</v>
       </c>
-      <c r="T6" s="30">
+      <c r="T8" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="U6" s="30">
+      <c r="U8" s="4">
+        <f t="shared" si="6"/>
+        <v>287.5</v>
+      </c>
+      <c r="V8" s="4">
+        <f t="shared" si="7"/>
+        <v>575</v>
+      </c>
+      <c r="W8" s="4">
+        <f t="shared" si="8"/>
+        <v>4.4809170779551302</v>
+      </c>
+      <c r="X8" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="Y8" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="9"/>
+        <v>10.5</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="4">
         <v>302.25</v>
       </c>
-      <c r="V6" s="30">
+      <c r="AJ8" s="4">
         <v>604.5</v>
       </c>
-      <c r="W6" s="30">
+      <c r="AK8" s="4">
         <v>4.2622450000000001</v>
       </c>
-      <c r="X6" s="30">
-        <v>0.4</v>
-      </c>
-      <c r="Y6" s="30">
+      <c r="AL8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM8" s="4">
         <v>35</v>
       </c>
-      <c r="Z6" s="30">
+      <c r="AN8" s="4">
         <v>10.5</v>
       </c>
-      <c r="AA6" s="30">
+      <c r="AO8" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AB6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="30">
+      <c r="AP8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F9" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G9" s="4">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="2"/>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" si="3"/>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J9" s="4">
+        <v>3</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="4"/>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="M9" s="4">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4">
+        <v>1200</v>
+      </c>
+      <c r="O9" s="4">
+        <f t="shared" si="5"/>
+        <v>1793.6842105263158</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="1"/>
+        <v>7.520833333333333</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R9" s="4">
+        <v>35</v>
+      </c>
+      <c r="S9" s="4">
+        <v>30</v>
+      </c>
+      <c r="T9" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U9" s="4">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="V9" s="4">
+        <f t="shared" si="7"/>
+        <v>600</v>
+      </c>
+      <c r="W9" s="4">
+        <f t="shared" si="8"/>
+        <v>4.2942121997069993</v>
+      </c>
+      <c r="X9" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="Y9" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="9"/>
+        <v>10.5</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="4">
         <v>302.25</v>
       </c>
-      <c r="AJ6" s="30">
+      <c r="AJ9" s="4">
         <v>604.5</v>
       </c>
-      <c r="AK6" s="30">
+      <c r="AK9" s="4">
         <v>4.2622450000000001</v>
       </c>
-      <c r="AL6" s="30">
+      <c r="AL9" s="4">
         <v>1</v>
       </c>
-      <c r="AM6" s="30">
+      <c r="AM9" s="4">
         <v>35</v>
       </c>
-      <c r="AN6" s="30">
+      <c r="AN9" s="4">
         <v>10.5</v>
       </c>
-      <c r="AO6" s="30">
+      <c r="AO9" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AP6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="30">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="30">
+      <c r="AP9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F10" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G10" s="4">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" si="2"/>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="3"/>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J10" s="4">
+        <v>4</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" si="4"/>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L10" s="4">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1250</v>
+      </c>
+      <c r="O10" s="4">
+        <f t="shared" si="5"/>
+        <v>1868.421052631579</v>
+      </c>
+      <c r="P10" s="4">
+        <f t="shared" si="1"/>
+        <v>7.22</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R10" s="4">
+        <v>35</v>
+      </c>
+      <c r="S10" s="4">
+        <v>30</v>
+      </c>
+      <c r="T10" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U10" s="4">
+        <f t="shared" si="6"/>
+        <v>312.5</v>
+      </c>
+      <c r="V10" s="4">
+        <f t="shared" si="7"/>
+        <v>625</v>
+      </c>
+      <c r="W10" s="4">
+        <f t="shared" si="8"/>
+        <v>4.12244371171872</v>
+      </c>
+      <c r="X10" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Y10" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="9"/>
+        <v>10.5</v>
+      </c>
+      <c r="AA10" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="4">
+        <v>302.25</v>
+      </c>
+      <c r="AJ10" s="4">
+        <v>604.5</v>
+      </c>
+      <c r="AK10" s="4">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL10" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="4">
+        <v>35</v>
+      </c>
+      <c r="AN10" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AO10" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.76</v>
+      </c>
+      <c r="F11" s="4">
+        <v>147.67060000000001</v>
+      </c>
+      <c r="G11" s="4">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" si="2"/>
+        <v>9.8447066666666672</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="3"/>
+        <v>176.71458676442586</v>
+      </c>
+      <c r="J11" s="4">
+        <v>5</v>
+      </c>
+      <c r="K11" s="4">
+        <f t="shared" si="4"/>
+        <v>6958.8130816679532</v>
+      </c>
+      <c r="L11" s="4">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4">
+        <v>1</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1300</v>
+      </c>
+      <c r="O11" s="4">
+        <f t="shared" si="5"/>
+        <v>1943.1578947368421</v>
+      </c>
+      <c r="P11" s="4">
+        <f t="shared" si="1"/>
+        <v>6.9423076923076925</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="R11" s="4">
+        <v>35</v>
+      </c>
+      <c r="S11" s="4">
+        <v>30</v>
+      </c>
+      <c r="T11" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U11" s="4">
+        <f t="shared" si="6"/>
+        <v>325</v>
+      </c>
+      <c r="V11" s="4">
+        <f t="shared" si="7"/>
+        <v>650</v>
+      </c>
+      <c r="W11" s="4">
+        <f t="shared" si="8"/>
+        <v>3.9638881843449227</v>
+      </c>
+      <c r="X11" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="Y11" s="4">
+        <f>35</f>
+        <v>35</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="9"/>
+        <v>10.5</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="4">
+        <v>302.25</v>
+      </c>
+      <c r="AJ11" s="4">
+        <v>604.5</v>
+      </c>
+      <c r="AK11" s="4">
+        <v>4.2622450000000001</v>
+      </c>
+      <c r="AL11" s="4">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="4">
+        <v>35</v>
+      </c>
+      <c r="AN11" s="4">
+        <v>10.5</v>
+      </c>
+      <c r="AO11" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AP11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="4">
         <v>0</v>
       </c>
     </row>
@@ -4135,7 +4960,7 @@
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$19</xm:f>
           </x14:formula1>
-          <xm:sqref>B7:B15</xm:sqref>
+          <xm:sqref>B12:B15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4661,164 +5486,163 @@
       <c r="A4" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="29">
         <v>0.11</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="29">
         <v>0.36</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="29">
         <v>-0.36480000000000001</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="29">
         <v>-0.22969999999999999</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="29">
         <v>-9.06E-2</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="29">
         <v>9.1499999999999998E-2</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="29">
         <v>0.25209999999999999</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="29">
         <v>0.3926</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="29">
         <v>0.4924</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="29">
         <v>0.59919999999999995</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="29">
         <v>0.70809999999999995</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="29">
         <v>0.81489999999999996</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="29">
         <v>0.92130000000000001</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="29">
         <v>1.0299</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="Q4" s="29">
         <v>1.1337999999999999</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="29">
         <v>1.2350000000000001</v>
       </c>
-      <c r="S4" s="10">
+      <c r="S4" s="29">
         <v>1.3317000000000001</v>
       </c>
-      <c r="T4" s="10">
+      <c r="T4" s="29">
         <v>1.4271</v>
       </c>
-      <c r="U4" s="10">
+      <c r="U4" s="29">
         <v>1.5059</v>
       </c>
-      <c r="V4" s="10">
+      <c r="V4" s="29">
         <v>1.5843</v>
       </c>
-      <c r="W4" s="10">
+      <c r="W4" s="29">
         <v>1.5843</v>
       </c>
-      <c r="X4" s="10">
+      <c r="X4" s="29">
         <v>1.2370000000000001E-2</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="Y4" s="29">
         <v>1.1509999999999999E-2</v>
       </c>
-      <c r="Z4" s="10">
+      <c r="Z4" s="29">
         <v>1.082E-2</v>
       </c>
-      <c r="AA4" s="10">
+      <c r="AA4" s="29">
         <v>9.1400000000000006E-3</v>
       </c>
-      <c r="AB4" s="10">
+      <c r="AB4" s="29">
         <v>6.3699999999999998E-3</v>
       </c>
-      <c r="AC4" s="10">
+      <c r="AC4" s="29">
         <v>8.1300000000000001E-3</v>
       </c>
-      <c r="AD4" s="10">
+      <c r="AD4" s="29">
         <v>1.027E-2</v>
       </c>
-      <c r="AE4" s="10">
+      <c r="AE4" s="29">
         <v>1.1220000000000001E-2</v>
       </c>
-      <c r="AF4" s="10">
+      <c r="AF4" s="29">
         <v>1.2160000000000001E-2</v>
       </c>
-      <c r="AG4" s="10">
+      <c r="AG4" s="29">
         <v>1.312E-2</v>
       </c>
-      <c r="AH4" s="10">
+      <c r="AH4" s="29">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="AI4" s="10">
+      <c r="AI4" s="29">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="AJ4" s="10">
+      <c r="AJ4" s="29">
         <v>1.651E-2</v>
       </c>
-      <c r="AK4" s="10">
+      <c r="AK4" s="29">
         <v>1.806E-2</v>
       </c>
-      <c r="AL4" s="10">
+      <c r="AL4" s="29">
         <v>1.9970000000000002E-2</v>
       </c>
-      <c r="AM4" s="10">
+      <c r="AM4" s="29">
         <v>2.1649999999999999E-2</v>
       </c>
-      <c r="AN4" s="10">
+      <c r="AN4" s="29">
         <v>2.487E-2</v>
       </c>
-      <c r="AO4" s="10">
+      <c r="AO4" s="29">
         <v>2.726E-2</v>
       </c>
-      <c r="AP4" s="10">
-        <f>MIN(X4:AO4)</f>
+      <c r="AP4" s="29">
         <v>6.3699999999999998E-3</v>
       </c>
-      <c r="AQ4" s="10" t="s">
+      <c r="AQ4" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="AR4" s="10">
+      <c r="AR4" s="29">
         <v>0.04</v>
       </c>
-      <c r="AS4" s="10">
+      <c r="AS4" s="29">
         <v>0.3</v>
       </c>
-      <c r="AT4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV4" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="10" t="s">
+      <c r="AT4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="AX4" s="10">
+      <c r="AX4" s="29">
         <v>0.04</v>
       </c>
-      <c r="AY4" s="10">
+      <c r="AY4" s="29">
         <v>0.3</v>
       </c>
-      <c r="AZ4" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA4" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB4" s="10">
+      <c r="AZ4" s="29">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="29">
+        <v>0</v>
+      </c>
+      <c r="BB4" s="29">
         <v>0</v>
       </c>
     </row>
@@ -4826,164 +5650,163 @@
       <c r="A5" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="29">
         <v>0.11</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="29">
         <v>0.36</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="29">
         <v>-0.36480000000000001</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="29">
         <v>-0.22969999999999999</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="29">
         <v>-9.06E-2</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="29">
         <v>9.1499999999999998E-2</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="29">
         <v>0.25209999999999999</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="29">
         <v>0.3926</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="29">
         <v>0.4924</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="29">
         <v>0.59919999999999995</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="29">
         <v>0.70809999999999995</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="29">
         <v>0.81489999999999996</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="29">
         <v>0.92130000000000001</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="29">
         <v>1.0299</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="29">
         <v>1.1337999999999999</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="29">
         <v>1.2350000000000001</v>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="29">
         <v>1.3317000000000001</v>
       </c>
-      <c r="T5" s="10">
+      <c r="T5" s="29">
         <v>1.4271</v>
       </c>
-      <c r="U5" s="10">
+      <c r="U5" s="29">
         <v>1.5059</v>
       </c>
-      <c r="V5" s="10">
+      <c r="V5" s="29">
         <v>1.5843</v>
       </c>
-      <c r="W5" s="10">
+      <c r="W5" s="29">
         <v>1.5843</v>
       </c>
-      <c r="X5" s="10">
+      <c r="X5" s="29">
         <v>1.2370000000000001E-2</v>
       </c>
-      <c r="Y5" s="10">
+      <c r="Y5" s="29">
         <v>1.1509999999999999E-2</v>
       </c>
-      <c r="Z5" s="10">
+      <c r="Z5" s="29">
         <v>1.082E-2</v>
       </c>
-      <c r="AA5" s="10">
+      <c r="AA5" s="29">
         <v>9.1400000000000006E-3</v>
       </c>
-      <c r="AB5" s="10">
+      <c r="AB5" s="29">
         <v>6.3699999999999998E-3</v>
       </c>
-      <c r="AC5" s="10">
+      <c r="AC5" s="29">
         <v>8.1300000000000001E-3</v>
       </c>
-      <c r="AD5" s="10">
+      <c r="AD5" s="29">
         <v>1.027E-2</v>
       </c>
-      <c r="AE5" s="10">
+      <c r="AE5" s="29">
         <v>1.1220000000000001E-2</v>
       </c>
-      <c r="AF5" s="10">
+      <c r="AF5" s="29">
         <v>1.2160000000000001E-2</v>
       </c>
-      <c r="AG5" s="10">
+      <c r="AG5" s="29">
         <v>1.312E-2</v>
       </c>
-      <c r="AH5" s="10">
+      <c r="AH5" s="29">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="AI5" s="10">
+      <c r="AI5" s="29">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="AJ5" s="10">
+      <c r="AJ5" s="29">
         <v>1.651E-2</v>
       </c>
-      <c r="AK5" s="10">
+      <c r="AK5" s="29">
         <v>1.806E-2</v>
       </c>
-      <c r="AL5" s="10">
+      <c r="AL5" s="29">
         <v>1.9970000000000002E-2</v>
       </c>
-      <c r="AM5" s="10">
+      <c r="AM5" s="29">
         <v>2.1649999999999999E-2</v>
       </c>
-      <c r="AN5" s="10">
+      <c r="AN5" s="29">
         <v>2.487E-2</v>
       </c>
-      <c r="AO5" s="10">
+      <c r="AO5" s="29">
         <v>2.726E-2</v>
       </c>
-      <c r="AP5" s="10">
-        <f>MIN(X5:AO5)</f>
+      <c r="AP5" s="29">
         <v>6.3699999999999998E-3</v>
       </c>
-      <c r="AQ5" s="10" t="s">
+      <c r="AQ5" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="AR5" s="10">
+      <c r="AR5" s="29">
         <v>0.04</v>
       </c>
-      <c r="AS5" s="10">
+      <c r="AS5" s="29">
         <v>0.3</v>
       </c>
-      <c r="AT5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="10" t="s">
+      <c r="AT5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="29">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="AX5" s="10">
+      <c r="AX5" s="29">
         <v>0.04</v>
       </c>
-      <c r="AY5" s="10">
+      <c r="AY5" s="29">
         <v>0.3</v>
       </c>
-      <c r="AZ5" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA5" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB5" s="10">
+      <c r="AZ5" s="29">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="29">
+        <v>0</v>
+      </c>
+      <c r="BB5" s="29">
         <v>0</v>
       </c>
     </row>
@@ -4991,164 +5814,985 @@
       <c r="A6" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="29">
         <v>0.11</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="29">
         <v>0.36</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="29">
         <v>-0.36480000000000001</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="29">
         <v>-0.22969999999999999</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="29">
         <v>-9.06E-2</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="29">
         <v>9.1499999999999998E-2</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="29">
         <v>0.25209999999999999</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="29">
         <v>0.3926</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="29">
         <v>0.4924</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="29">
         <v>0.59919999999999995</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="29">
         <v>0.70809999999999995</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="29">
         <v>0.81489999999999996</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="29">
         <v>0.92130000000000001</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="29">
         <v>1.0299</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="29">
         <v>1.1337999999999999</v>
       </c>
-      <c r="R6" s="10">
+      <c r="R6" s="29">
         <v>1.2350000000000001</v>
       </c>
-      <c r="S6" s="10">
+      <c r="S6" s="29">
         <v>1.3317000000000001</v>
       </c>
-      <c r="T6" s="10">
+      <c r="T6" s="29">
         <v>1.4271</v>
       </c>
-      <c r="U6" s="10">
+      <c r="U6" s="29">
         <v>1.5059</v>
       </c>
-      <c r="V6" s="10">
+      <c r="V6" s="29">
         <v>1.5843</v>
       </c>
-      <c r="W6" s="10">
+      <c r="W6" s="29">
         <v>1.5843</v>
       </c>
-      <c r="X6" s="10">
+      <c r="X6" s="29">
         <v>1.2370000000000001E-2</v>
       </c>
-      <c r="Y6" s="10">
+      <c r="Y6" s="29">
         <v>1.1509999999999999E-2</v>
       </c>
-      <c r="Z6" s="10">
+      <c r="Z6" s="29">
         <v>1.082E-2</v>
       </c>
-      <c r="AA6" s="10">
+      <c r="AA6" s="29">
         <v>9.1400000000000006E-3</v>
       </c>
-      <c r="AB6" s="10">
+      <c r="AB6" s="29">
         <v>6.3699999999999998E-3</v>
       </c>
-      <c r="AC6" s="10">
+      <c r="AC6" s="29">
         <v>8.1300000000000001E-3</v>
       </c>
-      <c r="AD6" s="10">
+      <c r="AD6" s="29">
         <v>1.027E-2</v>
       </c>
-      <c r="AE6" s="10">
+      <c r="AE6" s="29">
         <v>1.1220000000000001E-2</v>
       </c>
-      <c r="AF6" s="10">
+      <c r="AF6" s="29">
         <v>1.2160000000000001E-2</v>
       </c>
-      <c r="AG6" s="10">
+      <c r="AG6" s="29">
         <v>1.312E-2</v>
       </c>
-      <c r="AH6" s="10">
+      <c r="AH6" s="29">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="AI6" s="10">
+      <c r="AI6" s="29">
         <v>1.5100000000000001E-2</v>
       </c>
-      <c r="AJ6" s="10">
+      <c r="AJ6" s="29">
         <v>1.651E-2</v>
       </c>
-      <c r="AK6" s="10">
+      <c r="AK6" s="29">
         <v>1.806E-2</v>
       </c>
-      <c r="AL6" s="10">
+      <c r="AL6" s="29">
         <v>1.9970000000000002E-2</v>
       </c>
-      <c r="AM6" s="10">
+      <c r="AM6" s="29">
         <v>2.1649999999999999E-2</v>
       </c>
-      <c r="AN6" s="10">
+      <c r="AN6" s="29">
         <v>2.487E-2</v>
       </c>
-      <c r="AO6" s="10">
+      <c r="AO6" s="29">
         <v>2.726E-2</v>
       </c>
-      <c r="AP6" s="10">
-        <f>MIN(X6:AO6)</f>
+      <c r="AP6" s="29">
         <v>6.3699999999999998E-3</v>
       </c>
-      <c r="AQ6" s="10" t="s">
+      <c r="AQ6" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="AR6" s="10">
+      <c r="AR6" s="29">
         <v>0.04</v>
       </c>
-      <c r="AS6" s="10">
+      <c r="AS6" s="29">
         <v>0.3</v>
       </c>
-      <c r="AT6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="10" t="s">
+      <c r="AT6" s="29">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="29">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="29">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="AX6" s="10">
+      <c r="AX6" s="29">
         <v>0.04</v>
       </c>
-      <c r="AY6" s="10">
+      <c r="AY6" s="29">
         <v>0.3</v>
       </c>
-      <c r="AZ6" s="10">
-        <v>0</v>
-      </c>
-      <c r="BA6" s="10">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="10">
+      <c r="AZ6" s="29">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="29">
+        <v>0</v>
+      </c>
+      <c r="BB6" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E7" s="10">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F7" s="10">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G7" s="10">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H7" s="10">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P7" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R7" s="10">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S7" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T7" s="10">
+        <v>1.4271</v>
+      </c>
+      <c r="U7" s="10">
+        <v>1.5059</v>
+      </c>
+      <c r="V7" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="W7" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="X7" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB7" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC7" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD7" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP7" s="10">
+        <f>MIN(X7:AO7)</f>
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ7" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR7" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AS7" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX7" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AY7" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E8" s="10">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H8" s="10">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P8" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R8" s="10">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S8" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T8" s="10">
+        <v>1.4271</v>
+      </c>
+      <c r="U8" s="10">
+        <v>1.5059</v>
+      </c>
+      <c r="V8" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="W8" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="X8" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB8" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC8" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ8" s="10">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO8" s="10">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP8" s="10">
+        <f>MIN(X8:AO8)</f>
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR8" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AS8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX8" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AY8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0.11</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0.36</v>
+      </c>
+      <c r="E9" s="29">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F9" s="29">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G9" s="29">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H9" s="29">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I9" s="29">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J9" s="29">
+        <v>0.3926</v>
+      </c>
+      <c r="K9" s="29">
+        <v>0.4924</v>
+      </c>
+      <c r="L9" s="29">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M9" s="29">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N9" s="29">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O9" s="29">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P9" s="29">
+        <v>1.0299</v>
+      </c>
+      <c r="Q9" s="29">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R9" s="29">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S9" s="29">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T9" s="29">
+        <v>1.4271</v>
+      </c>
+      <c r="U9" s="29">
+        <v>1.5059</v>
+      </c>
+      <c r="V9" s="29">
+        <v>1.5843</v>
+      </c>
+      <c r="W9" s="29">
+        <v>1.5843</v>
+      </c>
+      <c r="X9" s="29">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y9" s="29">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z9" s="29">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA9" s="29">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB9" s="29">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC9" s="29">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD9" s="29">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE9" s="29">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF9" s="29">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG9" s="29">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH9" s="29">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI9" s="29">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ9" s="29">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK9" s="29">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL9" s="29">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM9" s="29">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN9" s="29">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO9" s="29">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP9" s="29">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ9" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR9" s="29">
+        <v>0.04</v>
+      </c>
+      <c r="AS9" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="AT9" s="29">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="29">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="29">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX9" s="29">
+        <v>0.04</v>
+      </c>
+      <c r="AY9" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="AZ9" s="29">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="29">
+        <v>0</v>
+      </c>
+      <c r="BB9" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="29">
+        <v>0.11</v>
+      </c>
+      <c r="D10" s="29">
+        <v>0.36</v>
+      </c>
+      <c r="E10" s="29">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F10" s="29">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G10" s="29">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H10" s="29">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I10" s="29">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J10" s="29">
+        <v>0.3926</v>
+      </c>
+      <c r="K10" s="29">
+        <v>0.4924</v>
+      </c>
+      <c r="L10" s="29">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M10" s="29">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N10" s="29">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O10" s="29">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P10" s="29">
+        <v>1.0299</v>
+      </c>
+      <c r="Q10" s="29">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R10" s="29">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S10" s="29">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T10" s="29">
+        <v>1.4271</v>
+      </c>
+      <c r="U10" s="29">
+        <v>1.5059</v>
+      </c>
+      <c r="V10" s="29">
+        <v>1.5843</v>
+      </c>
+      <c r="W10" s="29">
+        <v>1.5843</v>
+      </c>
+      <c r="X10" s="29">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y10" s="29">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z10" s="29">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA10" s="29">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB10" s="29">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC10" s="29">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD10" s="29">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE10" s="29">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF10" s="29">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG10" s="29">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH10" s="29">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI10" s="29">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ10" s="29">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK10" s="29">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL10" s="29">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM10" s="29">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN10" s="29">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO10" s="29">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP10" s="29">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ10" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR10" s="29">
+        <v>0.04</v>
+      </c>
+      <c r="AS10" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="AT10" s="29">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="29">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="29">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX10" s="29">
+        <v>0.04</v>
+      </c>
+      <c r="AY10" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="AZ10" s="29">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="29">
+        <v>0</v>
+      </c>
+      <c r="BB10" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="29">
+        <v>0.11</v>
+      </c>
+      <c r="D11" s="29">
+        <v>0.36</v>
+      </c>
+      <c r="E11" s="29">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F11" s="29">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G11" s="29">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H11" s="29">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I11" s="29">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J11" s="29">
+        <v>0.3926</v>
+      </c>
+      <c r="K11" s="29">
+        <v>0.4924</v>
+      </c>
+      <c r="L11" s="29">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M11" s="29">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N11" s="29">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O11" s="29">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P11" s="29">
+        <v>1.0299</v>
+      </c>
+      <c r="Q11" s="29">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R11" s="29">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S11" s="29">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T11" s="29">
+        <v>1.4271</v>
+      </c>
+      <c r="U11" s="29">
+        <v>1.5059</v>
+      </c>
+      <c r="V11" s="29">
+        <v>1.5843</v>
+      </c>
+      <c r="W11" s="29">
+        <v>1.5843</v>
+      </c>
+      <c r="X11" s="29">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y11" s="29">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z11" s="29">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA11" s="29">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB11" s="29">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC11" s="29">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD11" s="29">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE11" s="29">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF11" s="29">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG11" s="29">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH11" s="29">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI11" s="29">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ11" s="29">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK11" s="29">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL11" s="29">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM11" s="29">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN11" s="29">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO11" s="29">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP11" s="29">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ11" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR11" s="29">
+        <v>0.04</v>
+      </c>
+      <c r="AS11" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="AT11" s="29">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="29">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="29">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="AX11" s="29">
+        <v>0.04</v>
+      </c>
+      <c r="AY11" s="29">
+        <v>0.3</v>
+      </c>
+      <c r="AZ11" s="29">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="29">
+        <v>0</v>
+      </c>
+      <c r="BB11" s="29">
         <v>0</v>
       </c>
     </row>
@@ -5505,6 +7149,286 @@
         <v>0</v>
       </c>
       <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>19500</v>
+      </c>
+      <c r="E7">
+        <v>0.73</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>19500</v>
+      </c>
+      <c r="E8">
+        <v>0.73</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>19500</v>
+      </c>
+      <c r="E9">
+        <v>0.73</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>19500</v>
+      </c>
+      <c r="E10">
+        <v>0.73</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>19500</v>
+      </c>
+      <c r="E11">
+        <v>0.73</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
         <v>0</v>
       </c>
     </row>
